--- a/xy10102/output/model_metrics.xlsx
+++ b/xy10102/output/model_metrics.xlsx
@@ -49,31 +49,31 @@
     <t>高峰时段 MAE</t>
   </si>
   <si>
-    <t>36.1182</t>
-  </si>
-  <si>
-    <t>6.0098</t>
-  </si>
-  <si>
-    <t>4.0674</t>
-  </si>
-  <si>
-    <t>0.9725</t>
-  </si>
-  <si>
-    <t>0.1139</t>
-  </si>
-  <si>
-    <t>6.2130</t>
-  </si>
-  <si>
-    <t>0.2731</t>
-  </si>
-  <si>
-    <t>6.1297</t>
-  </si>
-  <si>
-    <t>4.6111</t>
+    <t>38.5640</t>
+  </si>
+  <si>
+    <t>6.2100</t>
+  </si>
+  <si>
+    <t>4.2490</t>
+  </si>
+  <si>
+    <t>0.9709</t>
+  </si>
+  <si>
+    <t>0.1175</t>
+  </si>
+  <si>
+    <t>6.4862</t>
+  </si>
+  <si>
+    <t>0.1942</t>
+  </si>
+  <si>
+    <t>7.1549</t>
+  </si>
+  <si>
+    <t>5.4144</t>
   </si>
 </sst>
 </file>
